--- a/branches/dependabot/github_actions/dev/actions-b6b232b097/mii-cm-onko-atc-transitions-2021.xlsx
+++ b/branches/dependabot/github_actions/dev/actions-b6b232b097/mii-cm-onko-atc-transitions-2021.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot.rc2</t>
   </si>
   <si>
     <t>Name</t>
